--- a/data_lake/datos_diarios_preliminares/dt=2026-07-16/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-16/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB94745-055D-44C5-9FF1-D1CBBC4DAB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7D9CE8-CFD7-4EAA-9EC5-A156F8866631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$X$1:$X$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$Y$1:$Y$210</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6348,8 +6348,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="101" width="32.42578125" style="50" customWidth="1"/>
-    <col min="102" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="102" width="32.42578125" style="50" customWidth="1"/>
+    <col min="103" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6674,7 +6674,9 @@
       <c r="X5" s="56">
         <v>28</v>
       </c>
-      <c r="Y5" s="56"/>
+      <c r="Y5" s="56">
+        <v>28.4</v>
+      </c>
       <c r="Z5" s="56"/>
       <c r="AA5" s="56"/>
       <c r="AB5" s="56"/>
@@ -6693,19 +6695,19 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>14</v>
-      </c>
-      <c r="AQ5" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v/>
+        <v>28.866666666666671</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.15321488897127</v>
       </c>
-      <c r="AS5" s="71" t="str">
+      <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v/>
+        <v>0.71345177769540058</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6781,7 +6783,9 @@
       <c r="X6" s="56">
         <v>28.4</v>
       </c>
-      <c r="Y6" s="56"/>
+      <c r="Y6" s="56">
+        <v>28.7</v>
+      </c>
       <c r="Z6" s="56"/>
       <c r="AA6" s="56"/>
       <c r="AB6" s="56"/>
@@ -6800,19 +6804,19 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ6" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>28.873333333333331</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.39523388894882</v>
       </c>
-      <c r="AS6" s="71" t="str">
+      <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.47809944438451168</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6888,7 +6892,9 @@
       <c r="X7" s="56">
         <v>33</v>
       </c>
-      <c r="Y7" s="56"/>
+      <c r="Y7" s="56">
+        <v>33.1</v>
+      </c>
       <c r="Z7" s="56"/>
       <c r="AA7" s="56"/>
       <c r="AB7" s="56"/>
@@ -6907,19 +6913,19 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ7" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>31.846666666666671</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>29.20018049155146</v>
       </c>
-      <c r="AS7" s="71" t="str">
+      <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.6464861751152107</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6995,7 +7001,9 @@
       <c r="X8" s="56">
         <v>30.2</v>
       </c>
-      <c r="Y8" s="56"/>
+      <c r="Y8" s="56">
+        <v>30.7</v>
+      </c>
       <c r="Z8" s="56"/>
       <c r="AA8" s="56"/>
       <c r="AB8" s="56"/>
@@ -7014,19 +7022,19 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ8" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.966666666666661</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.578539316171401</v>
       </c>
-      <c r="AS8" s="71" t="str">
+      <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.3881273504952603</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7102,7 +7110,9 @@
       <c r="X9" s="56">
         <v>30.8</v>
       </c>
-      <c r="Y9" s="56"/>
+      <c r="Y9" s="56">
+        <v>30.5</v>
+      </c>
       <c r="Z9" s="56"/>
       <c r="AA9" s="56"/>
       <c r="AB9" s="56"/>
@@ -7121,19 +7131,19 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ9" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.65333333333334</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>29.78746898263023</v>
       </c>
-      <c r="AS9" s="71" t="str">
+      <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>-0.13413564929689059</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7209,7 +7219,9 @@
       <c r="X10" s="56">
         <v>32.5</v>
       </c>
-      <c r="Y10" s="56"/>
+      <c r="Y10" s="56">
+        <v>33</v>
+      </c>
       <c r="Z10" s="56"/>
       <c r="AA10" s="56"/>
       <c r="AB10" s="56"/>
@@ -7228,19 +7240,19 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ10" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>31.793333333333337</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>30.079422034405059</v>
       </c>
-      <c r="AS10" s="71" t="str">
+      <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.7139112989282772</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7316,7 +7328,9 @@
       <c r="X11" s="56">
         <v>34.1</v>
       </c>
-      <c r="Y11" s="56"/>
+      <c r="Y11" s="56">
+        <v>34.4</v>
+      </c>
       <c r="Z11" s="56"/>
       <c r="AA11" s="56"/>
       <c r="AB11" s="56"/>
@@ -7335,19 +7349,19 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ11" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>33.053333333333327</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>30.003914077227851</v>
       </c>
-      <c r="AS11" s="71" t="str">
+      <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3.0494192561054767</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7423,7 +7437,9 @@
       <c r="X12" s="56">
         <v>31.8</v>
       </c>
-      <c r="Y12" s="56"/>
+      <c r="Y12" s="56">
+        <v>31.5</v>
+      </c>
       <c r="Z12" s="56"/>
       <c r="AA12" s="56"/>
       <c r="AB12" s="56"/>
@@ -7442,19 +7458,19 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ12" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>30.319999999999997</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.26566638931558</v>
       </c>
-      <c r="AS12" s="71" t="str">
+      <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.0543336106844166</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7530,7 +7546,9 @@
       <c r="X13" s="56">
         <v>31.3</v>
       </c>
-      <c r="Y13" s="56"/>
+      <c r="Y13" s="56">
+        <v>31.7</v>
+      </c>
       <c r="Z13" s="56"/>
       <c r="AA13" s="56"/>
       <c r="AB13" s="56"/>
@@ -7549,19 +7567,19 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ13" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>30.046666666666667</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.329394697812361</v>
       </c>
-      <c r="AS13" s="71" t="str">
+      <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.7172719688543054</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7637,7 +7655,9 @@
       <c r="X14" s="56">
         <v>23.2</v>
       </c>
-      <c r="Y14" s="56"/>
+      <c r="Y14" s="56">
+        <v>25.4</v>
+      </c>
       <c r="Z14" s="56"/>
       <c r="AA14" s="56"/>
       <c r="AB14" s="56"/>
@@ -7656,19 +7676,19 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ14" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>23.74</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>21.72154002389485</v>
       </c>
-      <c r="AS14" s="71" t="str">
+      <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.0184599761051487</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7744,7 +7764,9 @@
       <c r="X15" s="56">
         <v>29.4</v>
       </c>
-      <c r="Y15" s="56"/>
+      <c r="Y15" s="56">
+        <v>31.2</v>
+      </c>
       <c r="Z15" s="56"/>
       <c r="AA15" s="56"/>
       <c r="AB15" s="56"/>
@@ -7763,19 +7785,19 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ15" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.119999999999997</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.235505376344079</v>
       </c>
-      <c r="AS15" s="71" t="str">
+      <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.88449462365591813</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7851,7 +7873,9 @@
       <c r="X16" s="56">
         <v>30</v>
       </c>
-      <c r="Y16" s="56"/>
+      <c r="Y16" s="56">
+        <v>30.5</v>
+      </c>
       <c r="Z16" s="56"/>
       <c r="AA16" s="56"/>
       <c r="AB16" s="56"/>
@@ -7870,19 +7894,19 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ16" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>28.486666666666668</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.637652848402979</v>
       </c>
-      <c r="AS16" s="71" t="str">
+      <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.84901381826368905</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7958,7 +7982,9 @@
       <c r="X17" s="56">
         <v>25.6</v>
       </c>
-      <c r="Y17" s="56"/>
+      <c r="Y17" s="56">
+        <v>25.2</v>
+      </c>
       <c r="Z17" s="56"/>
       <c r="AA17" s="56"/>
       <c r="AB17" s="56"/>
@@ -7977,19 +8003,19 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ17" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>24.753333333333337</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>23.983623669156199</v>
       </c>
-      <c r="AS17" s="71" t="str">
+      <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.76970966417713882</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8065,7 +8091,9 @@
       <c r="X18" s="56">
         <v>18.600000000000001</v>
       </c>
-      <c r="Y18" s="56"/>
+      <c r="Y18" s="56">
+        <v>18.2</v>
+      </c>
       <c r="Z18" s="56"/>
       <c r="AA18" s="56"/>
       <c r="AB18" s="56"/>
@@ -8084,19 +8112,19 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ18" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>18.82</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>17.418351254480282</v>
       </c>
-      <c r="AS18" s="71" t="str">
+      <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.4016487455197186</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8172,7 +8200,9 @@
       <c r="X19" s="56">
         <v>26.2</v>
       </c>
-      <c r="Y19" s="56"/>
+      <c r="Y19" s="56">
+        <v>26.4</v>
+      </c>
       <c r="Z19" s="56"/>
       <c r="AA19" s="56"/>
       <c r="AB19" s="56"/>
@@ -8191,19 +8221,19 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ19" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>24.613333333333333</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>22.133534946236551</v>
       </c>
-      <c r="AS19" s="71" t="str">
+      <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.4797983870967819</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8279,7 +8309,9 @@
       <c r="X20" s="56">
         <v>24.4</v>
       </c>
-      <c r="Y20" s="56"/>
+      <c r="Y20" s="56">
+        <v>26</v>
+      </c>
       <c r="Z20" s="56"/>
       <c r="AA20" s="56"/>
       <c r="AB20" s="56"/>
@@ -8298,19 +8330,19 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ20" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>24.880000000000003</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>22.60766542597187</v>
       </c>
-      <c r="AS20" s="71" t="str">
+      <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.2723345740281324</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8386,7 +8418,9 @@
       <c r="X21" s="56">
         <v>28.1</v>
       </c>
-      <c r="Y21" s="56"/>
+      <c r="Y21" s="56">
+        <v>29.4</v>
+      </c>
       <c r="Z21" s="56"/>
       <c r="AA21" s="56"/>
       <c r="AB21" s="56"/>
@@ -8405,19 +8439,19 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ21" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>27.126666666666665</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.690081891757131</v>
       </c>
-      <c r="AS21" s="71" t="str">
+      <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.4365847749095337</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8493,7 +8527,9 @@
       <c r="X22" s="56">
         <v>11.7</v>
       </c>
-      <c r="Y22" s="56"/>
+      <c r="Y22" s="56">
+        <v>16</v>
+      </c>
       <c r="Z22" s="56"/>
       <c r="AA22" s="56"/>
       <c r="AB22" s="56"/>
@@ -8512,19 +8548,19 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ22" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>15.379999999999999</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>13.7803329197684</v>
       </c>
-      <c r="AS22" s="71" t="str">
+      <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.5996670802315993</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8600,7 +8636,9 @@
       <c r="X23" s="56">
         <v>26.2</v>
       </c>
-      <c r="Y23" s="56"/>
+      <c r="Y23" s="56">
+        <v>27.5</v>
+      </c>
       <c r="Z23" s="56"/>
       <c r="AA23" s="56"/>
       <c r="AB23" s="56"/>
@@ -8619,11 +8657,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ23" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>26.299999999999997</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8707,7 +8745,9 @@
       <c r="X24" s="56">
         <v>29.1</v>
       </c>
-      <c r="Y24" s="56"/>
+      <c r="Y24" s="56">
+        <v>31.1</v>
+      </c>
       <c r="Z24" s="56"/>
       <c r="AA24" s="56"/>
       <c r="AB24" s="56"/>
@@ -8726,19 +8766,19 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ24" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.286666666666672</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.36235848473612</v>
       </c>
-      <c r="AS24" s="71" t="str">
+      <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.92430818193055231</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8814,7 +8854,9 @@
       <c r="X25" s="56">
         <v>22.7</v>
       </c>
-      <c r="Y25" s="56"/>
+      <c r="Y25" s="56">
+        <v>22.9</v>
+      </c>
       <c r="Z25" s="56"/>
       <c r="AA25" s="56"/>
       <c r="AB25" s="56"/>
@@ -8833,19 +8875,19 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ25" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>22.199999999999996</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>19.9334244562022</v>
       </c>
-      <c r="AS25" s="71" t="str">
+      <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.2665755437977957</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8921,7 +8963,9 @@
       <c r="X26" s="56">
         <v>11.1</v>
       </c>
-      <c r="Y26" s="56"/>
+      <c r="Y26" s="56">
+        <v>11.7</v>
+      </c>
       <c r="Z26" s="56"/>
       <c r="AA26" s="56"/>
       <c r="AB26" s="56"/>
@@ -8940,19 +8984,19 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ26" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>11.69333333333333</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>10.370314900153589</v>
       </c>
-      <c r="AS26" s="71" t="str">
+      <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.3230184331797403</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9028,7 +9072,9 @@
       <c r="X27" s="56">
         <v>29.9</v>
       </c>
-      <c r="Y27" s="56"/>
+      <c r="Y27" s="56">
+        <v>28.6</v>
+      </c>
       <c r="Z27" s="56"/>
       <c r="AA27" s="56"/>
       <c r="AB27" s="56"/>
@@ -9047,19 +9093,19 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ27" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>28.213333333333331</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>26.988705969595848</v>
       </c>
-      <c r="AS27" s="71" t="str">
+      <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.2246273637374827</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9135,7 +9181,9 @@
       <c r="X28" s="56">
         <v>25.7</v>
       </c>
-      <c r="Y28" s="56"/>
+      <c r="Y28" s="56">
+        <v>27.9</v>
+      </c>
       <c r="Z28" s="56"/>
       <c r="AA28" s="56"/>
       <c r="AB28" s="56"/>
@@ -9154,19 +9202,19 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ28" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>26.240000000000002</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.751418551476942</v>
       </c>
-      <c r="AS28" s="71" t="str">
+      <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.4885814485230604</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9242,7 +9290,9 @@
       <c r="X29" s="56">
         <v>28.9</v>
       </c>
-      <c r="Y29" s="56"/>
+      <c r="Y29" s="56">
+        <v>28.7</v>
+      </c>
       <c r="Z29" s="56"/>
       <c r="AA29" s="56"/>
       <c r="AB29" s="56"/>
@@ -9261,19 +9311,19 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ29" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>27.453333333333333</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>26.954042214257239</v>
       </c>
-      <c r="AS29" s="71" t="str">
+      <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.49929111907609425</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9349,7 +9399,9 @@
       <c r="X30" s="56">
         <v>26.2</v>
       </c>
-      <c r="Y30" s="56"/>
+      <c r="Y30" s="56">
+        <v>25.3</v>
+      </c>
       <c r="Z30" s="56"/>
       <c r="AA30" s="56"/>
       <c r="AB30" s="56"/>
@@ -9368,19 +9420,19 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ30" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>25</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.518001483129371</v>
       </c>
-      <c r="AS30" s="71" t="str">
+      <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.48199851687062889</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -9456,7 +9508,9 @@
       <c r="X31" s="98">
         <v>26.6</v>
       </c>
-      <c r="Y31" s="98"/>
+      <c r="Y31" s="98">
+        <v>25.4</v>
+      </c>
       <c r="Z31" s="98"/>
       <c r="AA31" s="98"/>
       <c r="AB31" s="98"/>
@@ -9475,19 +9529,19 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ31" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>26.326666666666661</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.368948626045398</v>
       </c>
-      <c r="AS31" s="71" t="str">
+      <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.95771804062126265</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9563,7 +9617,9 @@
       <c r="X32" s="56">
         <v>20</v>
       </c>
-      <c r="Y32" s="56"/>
+      <c r="Y32" s="56">
+        <v>20.06666666666667</v>
+      </c>
       <c r="Z32" s="56"/>
       <c r="AA32" s="56"/>
       <c r="AB32" s="56"/>
@@ -9582,19 +9638,19 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ32" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>20.628888888888888</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>17.656856052108839</v>
       </c>
-      <c r="AS32" s="71" t="str">
+      <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.9720328367800484</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9667,7 +9723,9 @@
       <c r="W33" s="56">
         <v>28.4</v>
       </c>
-      <c r="X33" s="56"/>
+      <c r="X33" s="56">
+        <v>29.1</v>
+      </c>
       <c r="Y33" s="56"/>
       <c r="Z33" s="56"/>
       <c r="AA33" s="56"/>
@@ -9687,7 +9745,7 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ33" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9775,7 +9833,9 @@
       <c r="X34" s="56">
         <v>22.06666666666667</v>
       </c>
-      <c r="Y34" s="56"/>
+      <c r="Y34" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="Z34" s="56"/>
       <c r="AA34" s="56"/>
       <c r="AB34" s="56"/>
@@ -9794,19 +9854,19 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ34" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>21.408888888888892</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>19.787197591680322</v>
       </c>
-      <c r="AS34" s="71" t="str">
+      <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.6216912972085709</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9989,7 +10049,9 @@
       <c r="X36" s="56">
         <v>21</v>
       </c>
-      <c r="Y36" s="56"/>
+      <c r="Y36" s="56">
+        <v>20.55</v>
+      </c>
       <c r="Z36" s="56"/>
       <c r="AA36" s="56"/>
       <c r="AB36" s="56"/>
@@ -10008,19 +10070,19 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ36" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>20.22666666666667</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>18.99881106321839</v>
       </c>
-      <c r="AS36" s="71" t="str">
+      <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.2278556034482797</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10096,7 +10158,9 @@
       <c r="X37" s="56">
         <v>28.2</v>
       </c>
-      <c r="Y37" s="56"/>
+      <c r="Y37" s="56">
+        <v>27.1</v>
+      </c>
       <c r="Z37" s="56"/>
       <c r="AA37" s="56"/>
       <c r="AB37" s="56"/>
@@ -10115,19 +10179,19 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ37" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>27.373333333333335</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.886229873937381</v>
       </c>
-      <c r="AS37" s="71" t="str">
+      <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.4871034593959536</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10201,7 +10265,9 @@
         <v>16</v>
       </c>
       <c r="X38" s="56"/>
-      <c r="Y38" s="56"/>
+      <c r="Y38" s="56">
+        <v>16.100000000000001</v>
+      </c>
       <c r="Z38" s="56"/>
       <c r="AA38" s="56"/>
       <c r="AB38" s="56"/>
@@ -10220,7 +10286,7 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ38" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10306,7 +10372,9 @@
         <v>22.8</v>
       </c>
       <c r="X39" s="56"/>
-      <c r="Y39" s="56"/>
+      <c r="Y39" s="56">
+        <v>23</v>
+      </c>
       <c r="Z39" s="56"/>
       <c r="AA39" s="56"/>
       <c r="AB39" s="56"/>
@@ -10325,7 +10393,7 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ39" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10407,7 +10475,9 @@
       </c>
       <c r="W40" s="56"/>
       <c r="X40" s="56"/>
-      <c r="Y40" s="56"/>
+      <c r="Y40" s="56">
+        <v>25.2</v>
+      </c>
       <c r="Z40" s="56"/>
       <c r="AA40" s="56"/>
       <c r="AB40" s="56"/>
@@ -10426,7 +10496,7 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ40" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10514,7 +10584,9 @@
       <c r="X41" s="56">
         <v>21.266666666666669</v>
       </c>
-      <c r="Y41" s="56"/>
+      <c r="Y41" s="56">
+        <v>19.533333333333331</v>
+      </c>
       <c r="Z41" s="56"/>
       <c r="AA41" s="56"/>
       <c r="AB41" s="56"/>
@@ -10533,19 +10605,19 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ41" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>20.693333333333332</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>18.492109191327739</v>
       </c>
-      <c r="AS41" s="71" t="str">
+      <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.2012241420055929</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10621,7 +10693,9 @@
       <c r="X42" s="56">
         <v>28.95</v>
       </c>
-      <c r="Y42" s="56"/>
+      <c r="Y42" s="56">
+        <v>28.9</v>
+      </c>
       <c r="Z42" s="56"/>
       <c r="AA42" s="56"/>
       <c r="AB42" s="56"/>
@@ -10640,19 +10714,19 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ42" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>28.073333333333331</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.752685517058271</v>
       </c>
-      <c r="AS42" s="71" t="str">
+      <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.32064781627505923</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10724,7 +10798,9 @@
       <c r="X43" s="56">
         <v>29.85</v>
       </c>
-      <c r="Y43" s="56"/>
+      <c r="Y43" s="56">
+        <v>30.55</v>
+      </c>
       <c r="Z43" s="56"/>
       <c r="AA43" s="56"/>
       <c r="AB43" s="56"/>
@@ -10743,7 +10819,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10831,7 +10907,9 @@
       <c r="X44" s="56">
         <v>29.45</v>
       </c>
-      <c r="Y44" s="56"/>
+      <c r="Y44" s="56">
+        <v>31.35</v>
+      </c>
       <c r="Z44" s="56"/>
       <c r="AA44" s="56"/>
       <c r="AB44" s="56"/>
@@ -10850,19 +10928,19 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ44" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>28.333333333333329</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.342343444282822</v>
       </c>
-      <c r="AS44" s="71" t="str">
+      <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.99098988905050689</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10938,7 +11016,9 @@
       <c r="X45" s="56">
         <v>28.75</v>
       </c>
-      <c r="Y45" s="56"/>
+      <c r="Y45" s="56">
+        <v>29.55</v>
+      </c>
       <c r="Z45" s="56"/>
       <c r="AA45" s="56"/>
       <c r="AB45" s="56"/>
@@ -10957,19 +11037,19 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ45" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.018333333333334</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.906197631897481</v>
       </c>
-      <c r="AS45" s="71" t="str">
+      <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.1121357014358537</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11045,7 +11125,9 @@
       <c r="X46" s="56">
         <v>31.733333333333331</v>
       </c>
-      <c r="Y46" s="56"/>
+      <c r="Y46" s="56">
+        <v>31.7</v>
+      </c>
       <c r="Z46" s="56"/>
       <c r="AA46" s="56"/>
       <c r="AB46" s="56"/>
@@ -11064,19 +11146,19 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ46" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>30.217777777777776</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.968875859317389</v>
       </c>
-      <c r="AS46" s="71" t="str">
+      <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.2489019184603869</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11310,7 +11392,9 @@
       <c r="X49" s="56">
         <v>29.35</v>
       </c>
-      <c r="Y49" s="56"/>
+      <c r="Y49" s="56">
+        <v>31.25</v>
+      </c>
       <c r="Z49" s="56"/>
       <c r="AA49" s="56"/>
       <c r="AB49" s="56"/>
@@ -11329,19 +11413,19 @@
       <c r="AO49" s="56"/>
       <c r="AP49" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ49" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ49" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.66</v>
       </c>
       <c r="AR49" s="71">
         <f>IFERROR(VLOOKUP(A49,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.288690346031821</v>
       </c>
-      <c r="AS49" s="71" t="str">
+      <c r="AS49" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.3713096539681793</v>
       </c>
     </row>
     <row r="50" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11603,7 +11687,9 @@
       <c r="X52" s="56">
         <v>30.15</v>
       </c>
-      <c r="Y52" s="56"/>
+      <c r="Y52" s="56">
+        <v>30.65</v>
+      </c>
       <c r="Z52" s="56"/>
       <c r="AA52" s="56"/>
       <c r="AB52" s="56"/>
@@ -11622,19 +11708,19 @@
       <c r="AO52" s="56"/>
       <c r="AP52" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ52" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ52" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.27</v>
       </c>
       <c r="AR52" s="71">
         <f>IFERROR(VLOOKUP(A52,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.359246296590548</v>
       </c>
-      <c r="AS52" s="71" t="str">
+      <c r="AS52" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.9107537034094513</v>
       </c>
     </row>
     <row r="53" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11710,7 +11796,9 @@
       <c r="X53" s="56">
         <v>30.85</v>
       </c>
-      <c r="Y53" s="56"/>
+      <c r="Y53" s="56">
+        <v>31.7</v>
+      </c>
       <c r="Z53" s="56"/>
       <c r="AA53" s="56"/>
       <c r="AB53" s="56"/>
@@ -11729,19 +11817,19 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ53" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>30.353333333333335</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.498226025066419</v>
       </c>
-      <c r="AS53" s="71" t="str">
+      <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.8551073082669163</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11805,7 +11893,9 @@
       <c r="X54" s="56">
         <v>30.4</v>
       </c>
-      <c r="Y54" s="56"/>
+      <c r="Y54" s="56">
+        <v>33.200000000000003</v>
+      </c>
       <c r="Z54" s="56"/>
       <c r="AA54" s="56"/>
       <c r="AB54" s="56"/>
@@ -11824,7 +11914,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12177,7 +12267,9 @@
       <c r="X58" s="56">
         <v>29.625</v>
       </c>
-      <c r="Y58" s="56"/>
+      <c r="Y58" s="56">
+        <v>30.05</v>
+      </c>
       <c r="Z58" s="56"/>
       <c r="AA58" s="56"/>
       <c r="AB58" s="56"/>
@@ -12196,19 +12288,19 @@
       <c r="AO58" s="56"/>
       <c r="AP58" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ58" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ58" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>29.094999999999995</v>
       </c>
       <c r="AR58" s="71">
         <f>IFERROR(VLOOKUP(A58,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.11421982908216</v>
       </c>
-      <c r="AS58" s="71" t="str">
+      <c r="AS58" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.98078017091783565</v>
       </c>
     </row>
     <row r="59" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12375,7 +12467,9 @@
       <c r="X60" s="56">
         <v>27.45</v>
       </c>
-      <c r="Y60" s="56"/>
+      <c r="Y60" s="56">
+        <v>27</v>
+      </c>
       <c r="Z60" s="56"/>
       <c r="AA60" s="56"/>
       <c r="AB60" s="56"/>
@@ -12394,7 +12488,7 @@
       <c r="AO60" s="56"/>
       <c r="AP60" s="58">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ60" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12482,7 +12576,9 @@
       <c r="X61" s="56">
         <v>25.2</v>
       </c>
-      <c r="Y61" s="56"/>
+      <c r="Y61" s="56">
+        <v>26.6</v>
+      </c>
       <c r="Z61" s="56"/>
       <c r="AA61" s="56"/>
       <c r="AB61" s="56"/>
@@ -12501,19 +12597,19 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ61" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>25.617777777777782</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.539003939963891</v>
       </c>
-      <c r="AS61" s="71" t="str">
+      <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.0787738378138911</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12729,7 +12825,9 @@
       <c r="X64" s="56">
         <v>26.6</v>
       </c>
-      <c r="Y64" s="56"/>
+      <c r="Y64" s="56">
+        <v>25.8</v>
+      </c>
       <c r="Z64" s="56"/>
       <c r="AA64" s="56"/>
       <c r="AB64" s="56"/>
@@ -12748,7 +12846,7 @@
       <c r="AO64" s="56"/>
       <c r="AP64" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ64" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12836,7 +12934,9 @@
       <c r="X65" s="56">
         <v>26.5</v>
       </c>
-      <c r="Y65" s="56"/>
+      <c r="Y65" s="56">
+        <v>25.85</v>
+      </c>
       <c r="Z65" s="56"/>
       <c r="AA65" s="56"/>
       <c r="AB65" s="56"/>
@@ -12855,19 +12955,19 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ65" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>25.513333333333335</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.909114830278991</v>
       </c>
-      <c r="AS65" s="71" t="str">
+      <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.60421850305434432</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12935,7 +13035,9 @@
       <c r="X66" s="56">
         <v>25.7</v>
       </c>
-      <c r="Y66" s="56"/>
+      <c r="Y66" s="56">
+        <v>25.45</v>
+      </c>
       <c r="Z66" s="56"/>
       <c r="AA66" s="56"/>
       <c r="AB66" s="56"/>
@@ -12954,7 +13056,7 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ66" s="71" t="str">
         <f t="shared" si="1"/>
@@ -13042,7 +13144,9 @@
       <c r="X67" s="56">
         <v>25.95</v>
       </c>
-      <c r="Y67" s="56"/>
+      <c r="Y67" s="56">
+        <v>25.75</v>
+      </c>
       <c r="Z67" s="56"/>
       <c r="AA67" s="56"/>
       <c r="AB67" s="56"/>
@@ -13061,19 +13165,19 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ67" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>25.196666666666665</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.52508750274302</v>
       </c>
-      <c r="AS67" s="71" t="str">
+      <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.67157916392364569</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13147,7 +13251,9 @@
       <c r="X68" s="56">
         <v>24.824999999999999</v>
       </c>
-      <c r="Y68" s="56"/>
+      <c r="Y68" s="56">
+        <v>25.225000000000001</v>
+      </c>
       <c r="Z68" s="56"/>
       <c r="AA68" s="56"/>
       <c r="AB68" s="56"/>
@@ -13166,7 +13272,7 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ68" s="71" t="str">
         <f t="shared" si="1"/>
@@ -13238,11 +13344,17 @@
       <c r="T69" s="56">
         <v>26.86666666666666</v>
       </c>
-      <c r="U69" s="56"/>
+      <c r="U69" s="56">
+        <v>27.2</v>
+      </c>
       <c r="V69" s="56"/>
       <c r="W69" s="56"/>
-      <c r="X69" s="56"/>
-      <c r="Y69" s="56"/>
+      <c r="X69" s="56">
+        <v>25.4</v>
+      </c>
+      <c r="Y69" s="56">
+        <v>26.333333333333329</v>
+      </c>
       <c r="Z69" s="56"/>
       <c r="AA69" s="56"/>
       <c r="AB69" s="56"/>
@@ -13261,7 +13373,7 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ69" s="71" t="str">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
@@ -13349,7 +13461,9 @@
       <c r="X70" s="56">
         <v>27.13333333333334</v>
       </c>
-      <c r="Y70" s="56"/>
+      <c r="Y70" s="56">
+        <v>26.8</v>
+      </c>
       <c r="Z70" s="56"/>
       <c r="AA70" s="56"/>
       <c r="AB70" s="56"/>
@@ -13368,19 +13482,19 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ70" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>25.842222222222226</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.662442913653528</v>
       </c>
-      <c r="AS70" s="71" t="str">
+      <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.17977930856869762</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13452,7 +13566,9 @@
       <c r="X71" s="56">
         <v>24.566666666666659</v>
       </c>
-      <c r="Y71" s="56"/>
+      <c r="Y71" s="56">
+        <v>26.166666666666671</v>
+      </c>
       <c r="Z71" s="56"/>
       <c r="AA71" s="56"/>
       <c r="AB71" s="56"/>
@@ -13471,7 +13587,7 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ71" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13656,7 +13772,9 @@
       <c r="X73" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="Y73" s="56"/>
+      <c r="Y73" s="56">
+        <v>21.6</v>
+      </c>
       <c r="Z73" s="56"/>
       <c r="AA73" s="56"/>
       <c r="AB73" s="56"/>
@@ -13675,19 +13793,19 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ73" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>20.303333333333335</v>
       </c>
       <c r="AR73" s="71">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>19.99849874936011</v>
       </c>
-      <c r="AS73" s="71" t="str">
+      <c r="AS73" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.30483458397322494</v>
       </c>
     </row>
     <row r="74" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13763,7 +13881,9 @@
       <c r="X74" s="56">
         <v>14.06666666666667</v>
       </c>
-      <c r="Y74" s="56"/>
+      <c r="Y74" s="56">
+        <v>15.56666666666667</v>
+      </c>
       <c r="Z74" s="56"/>
       <c r="AA74" s="56"/>
       <c r="AB74" s="56"/>
@@ -13782,19 +13902,19 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ74" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>15.428888888888885</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.18104369196679</v>
       </c>
-      <c r="AS74" s="71" t="str">
+      <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.2478451969220945</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13870,7 +13990,9 @@
       <c r="X75" s="56">
         <v>19.850000000000001</v>
       </c>
-      <c r="Y75" s="56"/>
+      <c r="Y75" s="56">
+        <v>20.65</v>
+      </c>
       <c r="Z75" s="56"/>
       <c r="AA75" s="56"/>
       <c r="AB75" s="56"/>
@@ -13889,19 +14011,19 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ75" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>20.591666666666665</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>19.799966611526219</v>
       </c>
-      <c r="AS75" s="71" t="str">
+      <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.79170005514044561</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13977,7 +14099,9 @@
       <c r="X76" s="56">
         <v>23.2</v>
       </c>
-      <c r="Y76" s="56"/>
+      <c r="Y76" s="56">
+        <v>24.4</v>
+      </c>
       <c r="Z76" s="56"/>
       <c r="AA76" s="56"/>
       <c r="AB76" s="56"/>
@@ -13996,19 +14120,19 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ76" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>23.826666666666661</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>22.683240855978919</v>
       </c>
-      <c r="AS76" s="71" t="str">
+      <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.1434258106877415</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14084,7 +14208,9 @@
       <c r="X77" s="56">
         <v>30.7</v>
       </c>
-      <c r="Y77" s="56"/>
+      <c r="Y77" s="56">
+        <v>32.799999999999997</v>
+      </c>
       <c r="Z77" s="56"/>
       <c r="AA77" s="56"/>
       <c r="AB77" s="56"/>
@@ -14103,19 +14229,19 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ77" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>31.049999999999997</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>29.183929810522649</v>
       </c>
-      <c r="AS77" s="71" t="str">
+      <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.8660701894773482</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14185,7 +14311,9 @@
       <c r="X78" s="56">
         <v>29.93333333333333</v>
       </c>
-      <c r="Y78" s="56"/>
+      <c r="Y78" s="56">
+        <v>29.06666666666667</v>
+      </c>
       <c r="Z78" s="56"/>
       <c r="AA78" s="56"/>
       <c r="AB78" s="56"/>
@@ -14204,7 +14332,7 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ78" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14393,7 +14521,9 @@
       <c r="X80" s="56">
         <v>22.9</v>
       </c>
-      <c r="Y80" s="56"/>
+      <c r="Y80" s="56">
+        <v>24.5</v>
+      </c>
       <c r="Z80" s="56"/>
       <c r="AA80" s="56"/>
       <c r="AB80" s="56"/>
@@ -14412,7 +14542,7 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ80" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14500,7 +14630,9 @@
       <c r="X81" s="56">
         <v>26.333333333333329</v>
       </c>
-      <c r="Y81" s="56"/>
+      <c r="Y81" s="56">
+        <v>26.133333333333329</v>
+      </c>
       <c r="Z81" s="56"/>
       <c r="AA81" s="56"/>
       <c r="AB81" s="56"/>
@@ -14519,19 +14651,19 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ81" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ81" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>25.482222222222219</v>
       </c>
       <c r="AR81" s="71">
         <f>IFERROR(VLOOKUP(A81,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.173722457421579</v>
       </c>
-      <c r="AS81" s="71" t="str">
+      <c r="AS81" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.30849976480064001</v>
       </c>
     </row>
     <row r="82" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14967,7 +15099,9 @@
       <c r="X86" s="56">
         <v>33.25</v>
       </c>
-      <c r="Y86" s="56"/>
+      <c r="Y86" s="56">
+        <v>35.25</v>
+      </c>
       <c r="Z86" s="56"/>
       <c r="AA86" s="56"/>
       <c r="AB86" s="56"/>
@@ -14986,19 +15120,19 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ86" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>32.36</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>29.006189972462391</v>
       </c>
-      <c r="AS86" s="71" t="str">
+      <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3.3538100275376088</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15175,7 +15309,9 @@
       <c r="X88" s="56">
         <v>35.75</v>
       </c>
-      <c r="Y88" s="56"/>
+      <c r="Y88" s="56">
+        <v>35.85</v>
+      </c>
       <c r="Z88" s="56"/>
       <c r="AA88" s="56"/>
       <c r="AB88" s="56"/>
@@ -15194,7 +15330,7 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ88" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15282,7 +15418,9 @@
       <c r="X89" s="56">
         <v>33.75</v>
       </c>
-      <c r="Y89" s="56"/>
+      <c r="Y89" s="56">
+        <v>33.700000000000003</v>
+      </c>
       <c r="Z89" s="56"/>
       <c r="AA89" s="56"/>
       <c r="AB89" s="56"/>
@@ -15301,19 +15439,19 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ89" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>32.166666666666664</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>29.035060057912659</v>
       </c>
-      <c r="AS89" s="71" t="str">
+      <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3.1316066087540051</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15389,7 +15527,9 @@
       <c r="X90" s="56">
         <v>18.45</v>
       </c>
-      <c r="Y90" s="56"/>
+      <c r="Y90" s="56">
+        <v>17.25</v>
+      </c>
       <c r="Z90" s="56"/>
       <c r="AA90" s="56"/>
       <c r="AB90" s="56"/>
@@ -15408,19 +15548,19 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ90" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>17.766666666666666</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>16.163344086021471</v>
       </c>
-      <c r="AS90" s="71" t="str">
+      <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.6033225806451945</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15496,7 +15636,9 @@
       <c r="X91" s="56">
         <v>24.2</v>
       </c>
-      <c r="Y91" s="56"/>
+      <c r="Y91" s="56">
+        <v>24.8</v>
+      </c>
       <c r="Z91" s="56"/>
       <c r="AA91" s="56"/>
       <c r="AB91" s="56"/>
@@ -15515,19 +15657,19 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ91" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ91" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>23.679999999999996</v>
       </c>
       <c r="AR91" s="71">
         <f>IFERROR(VLOOKUP(A91,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>22.109487865869621</v>
       </c>
-      <c r="AS91" s="71" t="str">
+      <c r="AS91" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.5705121341303752</v>
       </c>
     </row>
     <row r="92" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15603,7 +15745,9 @@
       <c r="X92" s="56">
         <v>17.05</v>
       </c>
-      <c r="Y92" s="56"/>
+      <c r="Y92" s="56">
+        <v>17.850000000000001</v>
+      </c>
       <c r="Z92" s="56"/>
       <c r="AA92" s="56"/>
       <c r="AB92" s="56"/>
@@ -15622,19 +15766,19 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ92" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>17.501666666666669</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>16.095227145934569</v>
       </c>
-      <c r="AS92" s="71" t="str">
+      <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.4064395207320999</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15710,7 +15854,9 @@
       <c r="X93" s="56">
         <v>14.4</v>
       </c>
-      <c r="Y93" s="56"/>
+      <c r="Y93" s="56">
+        <v>15.15</v>
+      </c>
       <c r="Z93" s="56"/>
       <c r="AA93" s="56"/>
       <c r="AB93" s="56"/>
@@ -15729,19 +15875,19 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ93" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>14.423333333333334</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>13.63280813615186</v>
       </c>
-      <c r="AS93" s="71" t="str">
+      <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.79052519718147352</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15975,7 +16121,9 @@
       <c r="X96" s="56">
         <v>13.25</v>
       </c>
-      <c r="Y96" s="56"/>
+      <c r="Y96" s="56">
+        <v>13.6</v>
+      </c>
       <c r="Z96" s="56"/>
       <c r="AA96" s="56"/>
       <c r="AB96" s="56"/>
@@ -15994,11 +16142,11 @@
       <c r="AO96" s="56"/>
       <c r="AP96" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ96" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ96" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>13.146666666666668</v>
       </c>
       <c r="AR96" s="71" t="str">
         <f>IFERROR(VLOOKUP(A96,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16078,7 +16226,9 @@
       <c r="X97" s="56">
         <v>14.266666666666669</v>
       </c>
-      <c r="Y97" s="56"/>
+      <c r="Y97" s="56">
+        <v>15.46666666666667</v>
+      </c>
       <c r="Z97" s="56"/>
       <c r="AA97" s="56"/>
       <c r="AB97" s="56"/>
@@ -16097,7 +16247,7 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ97" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16179,7 +16329,9 @@
       <c r="X98" s="56">
         <v>16.266666666666669</v>
       </c>
-      <c r="Y98" s="56"/>
+      <c r="Y98" s="56">
+        <v>17.266666666666669</v>
+      </c>
       <c r="Z98" s="56"/>
       <c r="AA98" s="56"/>
       <c r="AB98" s="56"/>
@@ -16198,7 +16350,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16276,7 +16428,9 @@
       <c r="X99" s="56">
         <v>13.75</v>
       </c>
-      <c r="Y99" s="56"/>
+      <c r="Y99" s="56">
+        <v>13.95</v>
+      </c>
       <c r="Z99" s="56"/>
       <c r="AA99" s="56"/>
       <c r="AB99" s="56"/>
@@ -16295,7 +16449,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16379,7 +16533,9 @@
       <c r="X100" s="56">
         <v>12.133333333333329</v>
       </c>
-      <c r="Y100" s="56"/>
+      <c r="Y100" s="56">
+        <v>13.53333333333333</v>
+      </c>
       <c r="Z100" s="56"/>
       <c r="AA100" s="56"/>
       <c r="AB100" s="56"/>
@@ -16398,7 +16554,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16638,7 +16794,9 @@
       <c r="X103" s="56">
         <v>18.533333333333331</v>
       </c>
-      <c r="Y103" s="56"/>
+      <c r="Y103" s="56">
+        <v>18.399999999999999</v>
+      </c>
       <c r="Z103" s="56"/>
       <c r="AA103" s="56"/>
       <c r="AB103" s="56"/>
@@ -16657,7 +16815,7 @@
       <c r="AO103" s="56"/>
       <c r="AP103" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ103" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16806,7 +16964,9 @@
       <c r="X105" s="56">
         <v>14.93333333333333</v>
       </c>
-      <c r="Y105" s="56"/>
+      <c r="Y105" s="56">
+        <v>15.866666666666671</v>
+      </c>
       <c r="Z105" s="56"/>
       <c r="AA105" s="56"/>
       <c r="AB105" s="56"/>
@@ -16825,7 +16985,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16913,7 +17073,9 @@
       <c r="X106" s="56">
         <v>14.25</v>
       </c>
-      <c r="Y106" s="56"/>
+      <c r="Y106" s="56">
+        <v>13.65</v>
+      </c>
       <c r="Z106" s="56"/>
       <c r="AA106" s="56"/>
       <c r="AB106" s="56"/>
@@ -16932,19 +17094,19 @@
       <c r="AO106" s="56"/>
       <c r="AP106" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ106" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ106" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>13.876666666666665</v>
       </c>
       <c r="AR106" s="71">
         <f>IFERROR(VLOOKUP(A106,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>14.22903291473181</v>
       </c>
-      <c r="AS106" s="71" t="str">
+      <c r="AS106" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>-0.35236624806514527</v>
       </c>
     </row>
     <row r="107" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17020,7 +17182,9 @@
       <c r="X107" s="56">
         <v>14.35</v>
       </c>
-      <c r="Y107" s="56"/>
+      <c r="Y107" s="56">
+        <v>14.65</v>
+      </c>
       <c r="Z107" s="56"/>
       <c r="AA107" s="56"/>
       <c r="AB107" s="56"/>
@@ -17039,19 +17203,19 @@
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ107" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ107" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>14.363333333333333</v>
       </c>
       <c r="AR107" s="71">
         <f>IFERROR(VLOOKUP(A107,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>13.71376308750779</v>
       </c>
-      <c r="AS107" s="71" t="str">
+      <c r="AS107" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.64957024582554368</v>
       </c>
     </row>
     <row r="108" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17127,7 +17291,9 @@
       <c r="X108" s="56">
         <v>17.2</v>
       </c>
-      <c r="Y108" s="56"/>
+      <c r="Y108" s="56">
+        <v>17.866666666666671</v>
+      </c>
       <c r="Z108" s="56"/>
       <c r="AA108" s="56"/>
       <c r="AB108" s="56"/>
@@ -17146,19 +17312,19 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ108" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>17.377777777777776</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>16.934962038466889</v>
       </c>
-      <c r="AS108" s="71" t="str">
+      <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.44281573931088758</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17234,7 +17400,9 @@
       <c r="X109" s="56">
         <v>15.66666666666667</v>
       </c>
-      <c r="Y109" s="56"/>
+      <c r="Y109" s="56">
+        <v>16.333333333333329</v>
+      </c>
       <c r="Z109" s="56"/>
       <c r="AA109" s="56"/>
       <c r="AB109" s="56"/>
@@ -17253,19 +17421,19 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ109" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>15.742222222222226</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.502363523573189</v>
       </c>
-      <c r="AS109" s="71" t="str">
+      <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.23985869864903719</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17341,7 +17509,9 @@
       <c r="X110" s="56">
         <v>17.600000000000001</v>
       </c>
-      <c r="Y110" s="56"/>
+      <c r="Y110" s="56">
+        <v>17.266666666666669</v>
+      </c>
       <c r="Z110" s="56"/>
       <c r="AA110" s="56"/>
       <c r="AB110" s="56"/>
@@ -17360,19 +17530,19 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ110" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>17.497777777777777</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>16.37969626110208</v>
       </c>
-      <c r="AS110" s="71" t="str">
+      <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.1180815166756979</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17446,7 +17616,9 @@
       <c r="X111" s="56">
         <v>18.8</v>
       </c>
-      <c r="Y111" s="56"/>
+      <c r="Y111" s="56">
+        <v>19.93333333333333</v>
+      </c>
       <c r="Z111" s="56"/>
       <c r="AA111" s="56"/>
       <c r="AB111" s="56"/>
@@ -17465,7 +17637,7 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ111" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17644,7 +17816,9 @@
       <c r="X113" s="56">
         <v>27.75</v>
       </c>
-      <c r="Y113" s="56"/>
+      <c r="Y113" s="56">
+        <v>27.4</v>
+      </c>
       <c r="Z113" s="56"/>
       <c r="AA113" s="56"/>
       <c r="AB113" s="56"/>
@@ -17663,19 +17837,19 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ113" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>26.026666666666667</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.844479977753021</v>
       </c>
-      <c r="AS113" s="71" t="str">
+      <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.18218668891364587</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17751,7 +17925,9 @@
       <c r="X114" s="56">
         <v>18.533333333333331</v>
       </c>
-      <c r="Y114" s="56"/>
+      <c r="Y114" s="56">
+        <v>19.600000000000001</v>
+      </c>
       <c r="Z114" s="56"/>
       <c r="AA114" s="56"/>
       <c r="AB114" s="56"/>
@@ -17770,19 +17946,19 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ114" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ114" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>19.164444444444442</v>
       </c>
       <c r="AR114" s="71">
         <f>IFERROR(VLOOKUP(A114,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>18.39650516634082</v>
       </c>
-      <c r="AS114" s="71" t="str">
+      <c r="AS114" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.76793927810362206</v>
       </c>
     </row>
     <row r="115" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17858,7 +18034,9 @@
       <c r="X115" s="56">
         <v>27.666666666666671</v>
       </c>
-      <c r="Y115" s="56"/>
+      <c r="Y115" s="56">
+        <v>28.733333333333331</v>
+      </c>
       <c r="Z115" s="56"/>
       <c r="AA115" s="56"/>
       <c r="AB115" s="56"/>
@@ -17877,19 +18055,19 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ115" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>26.151111111111117</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.368839605734749</v>
       </c>
-      <c r="AS115" s="71" t="str">
+      <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0.78227150537636803</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17962,8 +18140,12 @@
       <c r="W116" s="56">
         <v>28.6</v>
       </c>
-      <c r="X116" s="56"/>
-      <c r="Y116" s="56"/>
+      <c r="X116" s="56">
+        <v>28.666666666666671</v>
+      </c>
+      <c r="Y116" s="56">
+        <v>29.6</v>
+      </c>
       <c r="Z116" s="56"/>
       <c r="AA116" s="56"/>
       <c r="AB116" s="56"/>
@@ -17982,19 +18164,19 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="AQ116" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>28.382222222222229</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.753279569892459</v>
       </c>
-      <c r="AS116" s="71" t="str">
+      <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2.6289426523297692</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18070,7 +18252,9 @@
       <c r="X117" s="56">
         <v>24.13333333333334</v>
       </c>
-      <c r="Y117" s="56"/>
+      <c r="Y117" s="56">
+        <v>23.666666666666671</v>
+      </c>
       <c r="Z117" s="56"/>
       <c r="AA117" s="56"/>
       <c r="AB117" s="56"/>
@@ -18089,19 +18273,19 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ117" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>23.20888888888889</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>21.728440860215009</v>
       </c>
-      <c r="AS117" s="71" t="str">
+      <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.4804480286738801</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18167,7 +18351,9 @@
       <c r="X118" s="56">
         <v>26.8</v>
       </c>
-      <c r="Y118" s="56"/>
+      <c r="Y118" s="56">
+        <v>28</v>
+      </c>
       <c r="Z118" s="56"/>
       <c r="AA118" s="56"/>
       <c r="AB118" s="56"/>
@@ -18186,7 +18372,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18537,7 +18723,9 @@
       <c r="X122" s="56">
         <v>16.133333333333329</v>
       </c>
-      <c r="Y122" s="56"/>
+      <c r="Y122" s="56">
+        <v>15.866666666666671</v>
+      </c>
       <c r="Z122" s="56"/>
       <c r="AA122" s="56"/>
       <c r="AB122" s="56"/>
@@ -18556,7 +18744,7 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ122" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18713,7 +18901,9 @@
         <v>11.133333333333329</v>
       </c>
       <c r="X124" s="56"/>
-      <c r="Y124" s="56"/>
+      <c r="Y124" s="56">
+        <v>11.866666666666671</v>
+      </c>
       <c r="Z124" s="56"/>
       <c r="AA124" s="56"/>
       <c r="AB124" s="56"/>
@@ -18732,7 +18922,7 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ124" s="71" t="str">
         <f t="shared" si="4"/>
@@ -19057,7 +19247,9 @@
       <c r="X128" s="56">
         <v>16.36666666666666</v>
       </c>
-      <c r="Y128" s="56"/>
+      <c r="Y128" s="56">
+        <v>16.333333333333329</v>
+      </c>
       <c r="Z128" s="56"/>
       <c r="AA128" s="56"/>
       <c r="AB128" s="56"/>
@@ -19076,19 +19268,19 @@
       <c r="AO128" s="56"/>
       <c r="AP128" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ128" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ128" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>15.904444444444444</v>
       </c>
       <c r="AR128" s="71">
         <f>IFERROR(VLOOKUP(A128,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>14.253242374467449</v>
       </c>
-      <c r="AS128" s="71" t="str">
+      <c r="AS128" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.6512020699769945</v>
       </c>
     </row>
     <row r="129" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19350,7 +19542,9 @@
       <c r="X131" s="56">
         <v>13.8</v>
       </c>
-      <c r="Y131" s="56"/>
+      <c r="Y131" s="56">
+        <v>14.1</v>
+      </c>
       <c r="Z131" s="56"/>
       <c r="AA131" s="56"/>
       <c r="AB131" s="56"/>
@@ -19369,19 +19563,19 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ131" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>13.96</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>12.63533977465384</v>
       </c>
-      <c r="AS131" s="71" t="str">
+      <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.324660225346161</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19457,7 +19651,9 @@
       <c r="X132" s="56">
         <v>17.93333333333333</v>
       </c>
-      <c r="Y132" s="56"/>
+      <c r="Y132" s="56">
+        <v>18.466666666666669</v>
+      </c>
       <c r="Z132" s="56"/>
       <c r="AA132" s="56"/>
       <c r="AB132" s="56"/>
@@ -19476,19 +19672,19 @@
       <c r="AO132" s="56"/>
       <c r="AP132" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ132" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ132" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>17.968888888888888</v>
       </c>
       <c r="AR132" s="71">
         <f>IFERROR(VLOOKUP(A132,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.582178842383669</v>
       </c>
-      <c r="AS132" s="71" t="str">
+      <c r="AS132" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2.3867100465052182</v>
       </c>
     </row>
     <row r="133" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19564,7 +19760,9 @@
       <c r="X133" s="56">
         <v>22.4</v>
       </c>
-      <c r="Y133" s="56"/>
+      <c r="Y133" s="56">
+        <v>22.55</v>
+      </c>
       <c r="Z133" s="56"/>
       <c r="AA133" s="56"/>
       <c r="AB133" s="56"/>
@@ -19583,19 +19781,19 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>14</v>
-      </c>
-      <c r="AQ133" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v/>
+        <v>21.083333333333332</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>18.681880637405129</v>
       </c>
-      <c r="AS133" s="71" t="str">
+      <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v/>
+        <v>2.401452695928203</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19671,7 +19869,9 @@
       <c r="X134" s="56">
         <v>10.93333333333333</v>
       </c>
-      <c r="Y134" s="56"/>
+      <c r="Y134" s="56">
+        <v>10.6</v>
+      </c>
       <c r="Z134" s="56"/>
       <c r="AA134" s="56"/>
       <c r="AB134" s="56"/>
@@ -19690,19 +19890,19 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ134" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>10.99111111111111</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>10.85765007415646</v>
       </c>
-      <c r="AS134" s="71" t="str">
+      <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.13346103695464961</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19857,7 +20057,9 @@
       <c r="X136" s="56">
         <v>22.8</v>
       </c>
-      <c r="Y136" s="56"/>
+      <c r="Y136" s="56">
+        <v>23.06666666666667</v>
+      </c>
       <c r="Z136" s="56"/>
       <c r="AA136" s="56"/>
       <c r="AB136" s="56"/>
@@ -19876,19 +20078,19 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ136" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ136" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>22.244444444444444</v>
       </c>
       <c r="AR136" s="71">
         <f>IFERROR(VLOOKUP(A136,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>20.010221097348399</v>
       </c>
-      <c r="AS136" s="71" t="str">
+      <c r="AS136" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2.2342233470960444</v>
       </c>
     </row>
     <row r="137" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19964,7 +20166,9 @@
       <c r="X137" s="56">
         <v>14.425000000000001</v>
       </c>
-      <c r="Y137" s="56"/>
+      <c r="Y137" s="56">
+        <v>14.675000000000001</v>
+      </c>
       <c r="Z137" s="56"/>
       <c r="AA137" s="56"/>
       <c r="AB137" s="56"/>
@@ -19983,19 +20187,19 @@
       <c r="AO137" s="56"/>
       <c r="AP137" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ137" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ137" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>14.036666666666669</v>
       </c>
       <c r="AR137" s="71">
         <f>IFERROR(VLOOKUP(A137,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>12.904217772834009</v>
       </c>
-      <c r="AS137" s="71" t="str">
+      <c r="AS137" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.1324488938326596</v>
       </c>
     </row>
     <row r="138" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20071,7 +20275,9 @@
       <c r="X138" s="56">
         <v>16.3</v>
       </c>
-      <c r="Y138" s="56"/>
+      <c r="Y138" s="56">
+        <v>17.350000000000001</v>
+      </c>
       <c r="Z138" s="56"/>
       <c r="AA138" s="56"/>
       <c r="AB138" s="56"/>
@@ -20090,19 +20296,19 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ138" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>16.823333333333334</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.594350571769921</v>
       </c>
-      <c r="AS138" s="71" t="str">
+      <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.2289827615634135</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20178,7 +20384,9 @@
       <c r="X139" s="56">
         <v>13.46666666666667</v>
       </c>
-      <c r="Y139" s="56"/>
+      <c r="Y139" s="56">
+        <v>14.266666666666669</v>
+      </c>
       <c r="Z139" s="56"/>
       <c r="AA139" s="56"/>
       <c r="AB139" s="56"/>
@@ -20197,19 +20405,19 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ139" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>13.586666666666668</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>12.014029396838049</v>
       </c>
-      <c r="AS139" s="71" t="str">
+      <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.5726372698286184</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20283,7 +20491,9 @@
       <c r="X140" s="56">
         <v>10.7</v>
       </c>
-      <c r="Y140" s="56"/>
+      <c r="Y140" s="56">
+        <v>12.05</v>
+      </c>
       <c r="Z140" s="56"/>
       <c r="AA140" s="56"/>
       <c r="AB140" s="56"/>
@@ -20302,7 +20512,7 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ140" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20390,7 +20600,9 @@
       <c r="X141" s="56">
         <v>28.2</v>
       </c>
-      <c r="Y141" s="56"/>
+      <c r="Y141" s="56">
+        <v>28.6</v>
+      </c>
       <c r="Z141" s="56"/>
       <c r="AA141" s="56"/>
       <c r="AB141" s="56"/>
@@ -20409,19 +20621,19 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ141" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>27.817777777777781</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.861940092165881</v>
       </c>
-      <c r="AS141" s="71" t="str">
+      <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.9558376856119004</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20497,7 +20709,9 @@
       <c r="X142" s="56">
         <v>15.46666666666667</v>
       </c>
-      <c r="Y142" s="56"/>
+      <c r="Y142" s="56">
+        <v>16.13333333333334</v>
+      </c>
       <c r="Z142" s="56"/>
       <c r="AA142" s="56"/>
       <c r="AB142" s="56"/>
@@ -20516,19 +20730,19 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ142" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>15.653333333333334</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.712885753914289</v>
       </c>
-      <c r="AS142" s="71" t="str">
+      <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-5.9552420580955001E-2</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20604,7 +20818,9 @@
       <c r="X143" s="56">
         <v>17.93333333333333</v>
       </c>
-      <c r="Y143" s="56"/>
+      <c r="Y143" s="56">
+        <v>20.2</v>
+      </c>
       <c r="Z143" s="56"/>
       <c r="AA143" s="56"/>
       <c r="AB143" s="56"/>
@@ -20623,19 +20839,19 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ143" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>19.373333333333331</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>19.042016534498121</v>
       </c>
-      <c r="AS143" s="71" t="str">
+      <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.33131679883521059</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20708,8 +20924,12 @@
       <c r="W144" s="56">
         <v>31.333333333333329</v>
       </c>
-      <c r="X144" s="56"/>
-      <c r="Y144" s="56"/>
+      <c r="X144" s="56">
+        <v>29.4</v>
+      </c>
+      <c r="Y144" s="56">
+        <v>31.533333333333331</v>
+      </c>
       <c r="Z144" s="56"/>
       <c r="AA144" s="56"/>
       <c r="AB144" s="56"/>
@@ -20728,19 +20948,19 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
-      </c>
-      <c r="AQ144" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>30.066666666666666</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.757199537797231</v>
       </c>
-      <c r="AS144" s="71" t="str">
+      <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.3094671288694357</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20816,7 +21036,9 @@
       <c r="X145" s="56">
         <v>24.733333333333331</v>
       </c>
-      <c r="Y145" s="56"/>
+      <c r="Y145" s="56">
+        <v>26</v>
+      </c>
       <c r="Z145" s="56"/>
       <c r="AA145" s="56"/>
       <c r="AB145" s="56"/>
@@ -20835,19 +21057,19 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ145" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>25.048888888888893</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>23.50405749186336</v>
       </c>
-      <c r="AS145" s="71" t="str">
+      <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.5448313970255327</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20921,7 +21143,9 @@
       <c r="X146" s="56">
         <v>32.200000000000003</v>
       </c>
-      <c r="Y146" s="56"/>
+      <c r="Y146" s="56">
+        <v>31.266666666666669</v>
+      </c>
       <c r="Z146" s="56"/>
       <c r="AA146" s="56"/>
       <c r="AB146" s="56"/>
@@ -20940,7 +21164,7 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ146" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21028,7 +21252,9 @@
       <c r="X147" s="56">
         <v>24.133333333333329</v>
       </c>
-      <c r="Y147" s="56"/>
+      <c r="Y147" s="56">
+        <v>24.6</v>
+      </c>
       <c r="Z147" s="56"/>
       <c r="AA147" s="56"/>
       <c r="AB147" s="56"/>
@@ -21047,19 +21273,19 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ147" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>23.604444444444443</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>21.876067772952851</v>
       </c>
-      <c r="AS147" s="71" t="str">
+      <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.728376671491592</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21214,7 +21440,9 @@
       <c r="X149" s="56">
         <v>23.4</v>
       </c>
-      <c r="Y149" s="56"/>
+      <c r="Y149" s="56">
+        <v>24.933333333333341</v>
+      </c>
       <c r="Z149" s="56"/>
       <c r="AA149" s="56"/>
       <c r="AB149" s="56"/>
@@ -21233,19 +21461,19 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ149" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>23.544444444444444</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>21.81258727862064</v>
       </c>
-      <c r="AS149" s="71" t="str">
+      <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.7318571658238042</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21479,7 +21707,9 @@
       <c r="X152" s="56">
         <v>21.25</v>
       </c>
-      <c r="Y152" s="56"/>
+      <c r="Y152" s="56">
+        <v>21.05</v>
+      </c>
       <c r="Z152" s="56"/>
       <c r="AA152" s="56"/>
       <c r="AB152" s="56"/>
@@ -21498,19 +21728,19 @@
       <c r="AO152" s="56"/>
       <c r="AP152" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ152" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ152" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>20.64</v>
       </c>
       <c r="AR152" s="71">
         <f>IFERROR(VLOOKUP(A152,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>19.513620754394939</v>
       </c>
-      <c r="AS152" s="71" t="str">
+      <c r="AS152" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.1263792456050616</v>
       </c>
     </row>
     <row r="153" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21586,7 +21816,9 @@
       <c r="X153" s="56">
         <v>30.06666666666667</v>
       </c>
-      <c r="Y153" s="56"/>
+      <c r="Y153" s="56">
+        <v>30.666666666666671</v>
+      </c>
       <c r="Z153" s="56"/>
       <c r="AA153" s="56"/>
       <c r="AB153" s="56"/>
@@ -21605,19 +21837,19 @@
       <c r="AO153" s="56"/>
       <c r="AP153" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ153" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ153" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>28.808888888888891</v>
       </c>
       <c r="AR153" s="71">
         <f>IFERROR(VLOOKUP(A153,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>27.722786560855798</v>
       </c>
-      <c r="AS153" s="71" t="str">
+      <c r="AS153" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.0861023280330926</v>
       </c>
     </row>
     <row r="154" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21766,7 +21998,9 @@
       <c r="X155" s="56">
         <v>29.6</v>
       </c>
-      <c r="Y155" s="56"/>
+      <c r="Y155" s="56">
+        <v>31.333333333333329</v>
+      </c>
       <c r="Z155" s="56"/>
       <c r="AA155" s="56"/>
       <c r="AB155" s="56"/>
@@ -21785,7 +22019,7 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ155" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21869,7 +22103,9 @@
       <c r="X156" s="56">
         <v>31.466666666666669</v>
       </c>
-      <c r="Y156" s="56"/>
+      <c r="Y156" s="56">
+        <v>31.266666666666669</v>
+      </c>
       <c r="Z156" s="56"/>
       <c r="AA156" s="56"/>
       <c r="AB156" s="56"/>
@@ -21888,7 +22124,7 @@
       <c r="AO156" s="56"/>
       <c r="AP156" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ156" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21972,7 +22208,9 @@
       <c r="X157" s="56">
         <v>20.6</v>
       </c>
-      <c r="Y157" s="56"/>
+      <c r="Y157" s="56">
+        <v>22.06666666666667</v>
+      </c>
       <c r="Z157" s="56"/>
       <c r="AA157" s="56"/>
       <c r="AB157" s="56"/>
@@ -21991,7 +22229,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22079,7 +22317,9 @@
       <c r="X158" s="56">
         <v>27.2</v>
       </c>
-      <c r="Y158" s="56"/>
+      <c r="Y158" s="56">
+        <v>27.466666666666669</v>
+      </c>
       <c r="Z158" s="56"/>
       <c r="AA158" s="56"/>
       <c r="AB158" s="56"/>
@@ -22098,11 +22338,11 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ158" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>27.102222222222228</v>
       </c>
       <c r="AR158" s="71" t="str">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22170,7 +22410,9 @@
       <c r="X159" s="56">
         <v>19.666666666666661</v>
       </c>
-      <c r="Y159" s="56"/>
+      <c r="Y159" s="56">
+        <v>20.93333333333333</v>
+      </c>
       <c r="Z159" s="56"/>
       <c r="AA159" s="56"/>
       <c r="AB159" s="56"/>
@@ -22189,7 +22431,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22277,7 +22519,9 @@
       <c r="X160" s="56">
         <v>30.06666666666667</v>
       </c>
-      <c r="Y160" s="56"/>
+      <c r="Y160" s="56">
+        <v>29.466666666666669</v>
+      </c>
       <c r="Z160" s="56"/>
       <c r="AA160" s="56"/>
       <c r="AB160" s="56"/>
@@ -22296,19 +22540,19 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ160" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29.053333333333331</v>
       </c>
       <c r="AR160" s="71">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.573537387874278</v>
       </c>
-      <c r="AS160" s="71" t="str">
+      <c r="AS160" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.47979594545905258</v>
       </c>
     </row>
     <row r="161" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22384,7 +22628,9 @@
       <c r="X161" s="56">
         <v>21.666666666666671</v>
       </c>
-      <c r="Y161" s="56"/>
+      <c r="Y161" s="56">
+        <v>22.13333333333334</v>
+      </c>
       <c r="Z161" s="56"/>
       <c r="AA161" s="56"/>
       <c r="AB161" s="56"/>
@@ -22403,19 +22649,19 @@
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ161" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ161" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>21.506666666666664</v>
       </c>
       <c r="AR161" s="71">
         <f>IFERROR(VLOOKUP(A161,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>21.249423815600579</v>
       </c>
-      <c r="AS161" s="71" t="str">
+      <c r="AS161" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.25724285106608491</v>
       </c>
     </row>
     <row r="162" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22491,7 +22737,9 @@
       <c r="X162" s="56">
         <v>25.8</v>
       </c>
-      <c r="Y162" s="56"/>
+      <c r="Y162" s="56">
+        <v>26.3</v>
+      </c>
       <c r="Z162" s="56"/>
       <c r="AA162" s="56"/>
       <c r="AB162" s="56"/>
@@ -22510,19 +22758,19 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ162" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>25.420000000000005</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>23.79792760916008</v>
       </c>
-      <c r="AS162" s="71" t="str">
+      <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.622072390839925</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22677,7 +22925,9 @@
       <c r="X164" s="56">
         <v>15.66666666666667</v>
       </c>
-      <c r="Y164" s="56"/>
+      <c r="Y164" s="56">
+        <v>15.266666666666669</v>
+      </c>
       <c r="Z164" s="56"/>
       <c r="AA164" s="56"/>
       <c r="AB164" s="56"/>
@@ -22696,19 +22946,19 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ164" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>15.075555555555557</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>13.598469534050141</v>
       </c>
-      <c r="AS164" s="71" t="str">
+      <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.477086021505416</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22780,7 +23030,9 @@
       <c r="X165" s="56">
         <v>20.8</v>
       </c>
-      <c r="Y165" s="56"/>
+      <c r="Y165" s="56">
+        <v>22</v>
+      </c>
       <c r="Z165" s="56"/>
       <c r="AA165" s="56"/>
       <c r="AB165" s="56"/>
@@ -22799,7 +23051,7 @@
       <c r="AO165" s="56"/>
       <c r="AP165" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ165" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22887,7 +23139,9 @@
       <c r="X166" s="56">
         <v>29.65</v>
       </c>
-      <c r="Y166" s="56"/>
+      <c r="Y166" s="56">
+        <v>29.15</v>
+      </c>
       <c r="Z166" s="56"/>
       <c r="AA166" s="56"/>
       <c r="AB166" s="56"/>
@@ -22906,19 +23160,19 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ166" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>28.20333333333333</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>26.065864466066579</v>
       </c>
-      <c r="AS166" s="71" t="str">
+      <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2.137468867266751</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22994,7 +23248,9 @@
       <c r="X167" s="56">
         <v>9</v>
       </c>
-      <c r="Y167" s="56"/>
+      <c r="Y167" s="56">
+        <v>8.8500000000000014</v>
+      </c>
       <c r="Z167" s="56"/>
       <c r="AA167" s="56"/>
       <c r="AB167" s="56"/>
@@ -23013,19 +23269,19 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ167" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>8.7766666666666655</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>8.5421242813545373</v>
       </c>
-      <c r="AS167" s="71" t="str">
+      <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.23454238531212823</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23091,7 +23347,9 @@
       <c r="X168" s="56">
         <v>24.733333333333331</v>
       </c>
-      <c r="Y168" s="56"/>
+      <c r="Y168" s="56">
+        <v>26.266666666666669</v>
+      </c>
       <c r="Z168" s="56"/>
       <c r="AA168" s="56"/>
       <c r="AB168" s="56"/>
@@ -23110,7 +23368,7 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ168" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23196,7 +23454,9 @@
         <v>20.666666666666671</v>
       </c>
       <c r="X169" s="56"/>
-      <c r="Y169" s="56"/>
+      <c r="Y169" s="56">
+        <v>22.933333333333341</v>
+      </c>
       <c r="Z169" s="56"/>
       <c r="AA169" s="56"/>
       <c r="AB169" s="56"/>
@@ -23215,7 +23475,7 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ169" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23299,7 +23559,9 @@
       <c r="X170" s="56">
         <v>27.15</v>
       </c>
-      <c r="Y170" s="56"/>
+      <c r="Y170" s="56">
+        <v>27.45</v>
+      </c>
       <c r="Z170" s="56"/>
       <c r="AA170" s="56"/>
       <c r="AB170" s="56"/>
@@ -23318,7 +23580,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23406,7 +23668,9 @@
       <c r="X171" s="56">
         <v>25.15</v>
       </c>
-      <c r="Y171" s="56"/>
+      <c r="Y171" s="56">
+        <v>26.15</v>
+      </c>
       <c r="Z171" s="56"/>
       <c r="AA171" s="56"/>
       <c r="AB171" s="56"/>
@@ -23425,19 +23689,19 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ171" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>25.292222222222222</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.054408602150531</v>
       </c>
-      <c r="AS171" s="71" t="str">
+      <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.2378136200716909</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23511,7 +23775,9 @@
       <c r="X172" s="56">
         <v>14.53333333333333</v>
       </c>
-      <c r="Y172" s="56"/>
+      <c r="Y172" s="56">
+        <v>14.8</v>
+      </c>
       <c r="Z172" s="56"/>
       <c r="AA172" s="56"/>
       <c r="AB172" s="56"/>
@@ -23530,7 +23796,7 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ172" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23972,7 +24238,9 @@
       <c r="X177" s="56">
         <v>19.7</v>
       </c>
-      <c r="Y177" s="56"/>
+      <c r="Y177" s="56">
+        <v>20.149999999999999</v>
+      </c>
       <c r="Z177" s="56"/>
       <c r="AA177" s="56"/>
       <c r="AB177" s="56"/>
@@ -23991,7 +24259,7 @@
       <c r="AO177" s="56"/>
       <c r="AP177" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ177" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24158,7 +24426,9 @@
       <c r="X179" s="56">
         <v>30.8</v>
       </c>
-      <c r="Y179" s="56"/>
+      <c r="Y179" s="56">
+        <v>31.6</v>
+      </c>
       <c r="Z179" s="56"/>
       <c r="AA179" s="56"/>
       <c r="AB179" s="56"/>
@@ -24177,19 +24447,19 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ179" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>30.94222222222222</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.533236387569811</v>
       </c>
-      <c r="AS179" s="71" t="str">
+      <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2.4089858346524089</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24423,7 +24693,9 @@
       <c r="X182" s="56">
         <v>27.733333333333331</v>
       </c>
-      <c r="Y182" s="56"/>
+      <c r="Y182" s="56">
+        <v>29</v>
+      </c>
       <c r="Z182" s="56"/>
       <c r="AA182" s="56"/>
       <c r="AB182" s="56"/>
@@ -24442,19 +24714,19 @@
       <c r="AO182" s="56"/>
       <c r="AP182" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ182" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ182" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>27.951111111111114</v>
       </c>
       <c r="AR182" s="71">
         <f>IFERROR(VLOOKUP(A182,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>26.638371217616989</v>
       </c>
-      <c r="AS182" s="71" t="str">
+      <c r="AS182" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.3127398934941255</v>
       </c>
     </row>
     <row r="183" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24522,7 +24794,9 @@
       <c r="V183" s="56"/>
       <c r="W183" s="56"/>
       <c r="X183" s="56"/>
-      <c r="Y183" s="56"/>
+      <c r="Y183" s="56">
+        <v>29.93333333333333</v>
+      </c>
       <c r="Z183" s="56"/>
       <c r="AA183" s="56"/>
       <c r="AB183" s="56"/>
@@ -24541,7 +24815,7 @@
       <c r="AO183" s="56"/>
       <c r="AP183" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ183" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24787,7 +25061,9 @@
       <c r="X186" s="56">
         <v>17.86666666666666</v>
       </c>
-      <c r="Y186" s="56"/>
+      <c r="Y186" s="56">
+        <v>17.733333333333331</v>
+      </c>
       <c r="Z186" s="56"/>
       <c r="AA186" s="56"/>
       <c r="AB186" s="56"/>
@@ -24806,19 +25082,19 @@
       <c r="AO186" s="56"/>
       <c r="AP186" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ186" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ186" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>17.408888888888892</v>
       </c>
       <c r="AR186" s="71">
         <f>IFERROR(VLOOKUP(A186,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.99559198953173</v>
       </c>
-      <c r="AS186" s="71" t="str">
+      <c r="AS186" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.413296899357162</v>
       </c>
     </row>
     <row r="187" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24886,7 +25162,9 @@
         <v>32.333333333333343</v>
       </c>
       <c r="X187" s="56"/>
-      <c r="Y187" s="56"/>
+      <c r="Y187" s="56">
+        <v>34.06666666666667</v>
+      </c>
       <c r="Z187" s="56"/>
       <c r="AA187" s="56"/>
       <c r="AB187" s="56"/>
@@ -24905,7 +25183,7 @@
       <c r="AO187" s="56"/>
       <c r="AP187" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ187" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24993,7 +25271,9 @@
       <c r="X188" s="56">
         <v>31.066666666666659</v>
       </c>
-      <c r="Y188" s="56"/>
+      <c r="Y188" s="56">
+        <v>32.200000000000003</v>
+      </c>
       <c r="Z188" s="56"/>
       <c r="AA188" s="56"/>
       <c r="AB188" s="56"/>
@@ -25012,19 +25292,19 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ188" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>30.586666666666666</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.916523661482469</v>
       </c>
-      <c r="AS188" s="71" t="str">
+      <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.6701430051841974</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25100,7 +25380,9 @@
       <c r="X189" s="56">
         <v>18.149999999999999</v>
       </c>
-      <c r="Y189" s="56"/>
+      <c r="Y189" s="56">
+        <v>18.850000000000001</v>
+      </c>
       <c r="Z189" s="56"/>
       <c r="AA189" s="56"/>
       <c r="AB189" s="56"/>
@@ -25119,19 +25401,19 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ189" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>18.683333333333334</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>17.387219014660609</v>
       </c>
-      <c r="AS189" s="71" t="str">
+      <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.2961143186727249</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25207,7 +25489,9 @@
       <c r="X190" s="56">
         <v>26.06666666666667</v>
       </c>
-      <c r="Y190" s="56"/>
+      <c r="Y190" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="Z190" s="56"/>
       <c r="AA190" s="56"/>
       <c r="AB190" s="56"/>
@@ -25226,19 +25510,19 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ190" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>26.248888888888892</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.244507180818172</v>
       </c>
-      <c r="AS190" s="71" t="str">
+      <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.0043817080707207</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25312,7 +25596,9 @@
       <c r="X191" s="56">
         <v>26.15</v>
       </c>
-      <c r="Y191" s="56"/>
+      <c r="Y191" s="56">
+        <v>28.75</v>
+      </c>
       <c r="Z191" s="56"/>
       <c r="AA191" s="56"/>
       <c r="AB191" s="56"/>
@@ -25331,7 +25617,7 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ191" s="71" t="str">
         <f t="shared" si="7"/>
@@ -25419,7 +25705,9 @@
       <c r="X192" s="56">
         <v>20.333333333333339</v>
       </c>
-      <c r="Y192" s="56"/>
+      <c r="Y192" s="56">
+        <v>22.2</v>
+      </c>
       <c r="Z192" s="56"/>
       <c r="AA192" s="56"/>
       <c r="AB192" s="56"/>
@@ -25438,19 +25726,19 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ192" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>21.306666666666668</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>21.60766179705843</v>
       </c>
-      <c r="AS192" s="71" t="str">
+      <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-0.30099513039176173</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25526,7 +25814,9 @@
       <c r="X193" s="56">
         <v>27.533333333333331</v>
       </c>
-      <c r="Y193" s="56"/>
+      <c r="Y193" s="56">
+        <v>28.86666666666666</v>
+      </c>
       <c r="Z193" s="56"/>
       <c r="AA193" s="56"/>
       <c r="AB193" s="56"/>
@@ -25545,19 +25835,19 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ193" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>27.866666666666667</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.687488209709759</v>
       </c>
-      <c r="AS193" s="71" t="str">
+      <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2.1791784569569081</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25633,7 +25923,9 @@
       <c r="X194" s="56">
         <v>22.8</v>
       </c>
-      <c r="Y194" s="56"/>
+      <c r="Y194" s="56">
+        <v>22.6</v>
+      </c>
       <c r="Z194" s="56"/>
       <c r="AA194" s="56"/>
       <c r="AB194" s="56"/>
@@ -25652,19 +25944,19 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ194" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>22.426666666666669</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>20.22375647152527</v>
       </c>
-      <c r="AS194" s="71" t="str">
+      <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2.2029101951413992</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25740,7 +26032,9 @@
       <c r="X195" s="56">
         <v>26.13333333333334</v>
       </c>
-      <c r="Y195" s="56"/>
+      <c r="Y195" s="56">
+        <v>27.13333333333334</v>
+      </c>
       <c r="Z195" s="56"/>
       <c r="AA195" s="56"/>
       <c r="AB195" s="56"/>
@@ -25759,19 +26053,19 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ195" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>25.844444444444441</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.127383001170529</v>
       </c>
-      <c r="AS195" s="71" t="str">
+      <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.7170614432739129</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25847,7 +26141,9 @@
       <c r="X196" s="56">
         <v>21.5</v>
       </c>
-      <c r="Y196" s="56"/>
+      <c r="Y196" s="56">
+        <v>22.75</v>
+      </c>
       <c r="Z196" s="56"/>
       <c r="AA196" s="56"/>
       <c r="AB196" s="56"/>
@@ -25866,11 +26162,11 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ196" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>21.706666666666663</v>
       </c>
       <c r="AR196" s="71" t="str">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25954,7 +26250,9 @@
       <c r="X197" s="56">
         <v>16.399999999999999</v>
       </c>
-      <c r="Y197" s="56"/>
+      <c r="Y197" s="56">
+        <v>17.13333333333334</v>
+      </c>
       <c r="Z197" s="56"/>
       <c r="AA197" s="56"/>
       <c r="AB197" s="56"/>
@@ -25973,19 +26271,19 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>14</v>
-      </c>
-      <c r="AQ197" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ197" s="71">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v/>
+        <v>16.662222222222226</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>15.78766040619119</v>
       </c>
-      <c r="AS197" s="71" t="str">
+      <c r="AS197" s="71">
         <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v/>
+        <v>0.87456181603103644</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26061,7 +26359,9 @@
       <c r="X198" s="56">
         <v>14.55</v>
       </c>
-      <c r="Y198" s="56"/>
+      <c r="Y198" s="56">
+        <v>15.15</v>
+      </c>
       <c r="Z198" s="56"/>
       <c r="AA198" s="56"/>
       <c r="AB198" s="56"/>
@@ -26080,19 +26380,19 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ198" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>14.626666666666669</v>
       </c>
       <c r="AR198" s="71">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>13.36561246778364</v>
       </c>
-      <c r="AS198" s="71" t="str">
+      <c r="AS198" s="71">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1.2610541988830288</v>
       </c>
     </row>
     <row r="199" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26168,7 +26468,9 @@
       <c r="X199" s="56">
         <v>27.4</v>
       </c>
-      <c r="Y199" s="56"/>
+      <c r="Y199" s="56">
+        <v>28.75</v>
+      </c>
       <c r="Z199" s="56"/>
       <c r="AA199" s="56"/>
       <c r="AB199" s="56"/>
@@ -26187,19 +26489,19 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ199" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>27.143333333333331</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>25.53752926833085</v>
       </c>
-      <c r="AS199" s="71" t="str">
+      <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1.6058040650024807</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26275,7 +26577,9 @@
       <c r="X200" s="56">
         <v>12.7</v>
       </c>
-      <c r="Y200" s="56"/>
+      <c r="Y200" s="56">
+        <v>12.85</v>
+      </c>
       <c r="Z200" s="56"/>
       <c r="AA200" s="56"/>
       <c r="AB200" s="56"/>
@@ -26294,19 +26598,19 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ200" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>13.446666666666665</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>12.80356395850392</v>
       </c>
-      <c r="AS200" s="71" t="str">
+      <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0.64310270816274517</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26583,7 +26887,9 @@
       <c r="W203" s="56">
         <v>14.45</v>
       </c>
-      <c r="X203" s="56"/>
+      <c r="X203" s="56">
+        <v>14.65</v>
+      </c>
       <c r="Y203" s="56"/>
       <c r="Z203" s="56"/>
       <c r="AA203" s="56"/>
@@ -26603,7 +26909,7 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ203" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26680,9 +26986,15 @@
         <v>13.45</v>
       </c>
       <c r="U204" s="56"/>
-      <c r="V204" s="56"/>
-      <c r="W204" s="56"/>
-      <c r="X204" s="56"/>
+      <c r="V204" s="56">
+        <v>13.8</v>
+      </c>
+      <c r="W204" s="56">
+        <v>13.45</v>
+      </c>
+      <c r="X204" s="56">
+        <v>12.4</v>
+      </c>
       <c r="Y204" s="56"/>
       <c r="Z204" s="56"/>
       <c r="AA204" s="56"/>
@@ -26702,7 +27014,7 @@
       <c r="AO204" s="56"/>
       <c r="AP204" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AQ204" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26782,7 +27094,9 @@
       <c r="X205" s="56">
         <v>13.2</v>
       </c>
-      <c r="Y205" s="56"/>
+      <c r="Y205" s="56">
+        <v>14.4</v>
+      </c>
       <c r="Z205" s="56"/>
       <c r="AA205" s="56"/>
       <c r="AB205" s="56"/>
@@ -26801,7 +27115,7 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ205" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26887,7 +27201,9 @@
       <c r="X206" s="56">
         <v>13.15</v>
       </c>
-      <c r="Y206" s="56"/>
+      <c r="Y206" s="56">
+        <v>14.75</v>
+      </c>
       <c r="Z206" s="56"/>
       <c r="AA206" s="56"/>
       <c r="AB206" s="56"/>
@@ -26906,7 +27222,7 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ206" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26994,7 +27310,9 @@
       <c r="X207" s="56">
         <v>10.35</v>
       </c>
-      <c r="Y207" s="56"/>
+      <c r="Y207" s="56">
+        <v>10.8</v>
+      </c>
       <c r="Z207" s="56"/>
       <c r="AA207" s="56"/>
       <c r="AB207" s="56"/>
@@ -27013,11 +27331,11 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ207" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>10.97</v>
       </c>
       <c r="AR207" s="71" t="str">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27098,7 +27416,9 @@
       <c r="W208" s="56">
         <v>15</v>
       </c>
-      <c r="X208" s="56"/>
+      <c r="X208" s="56">
+        <v>14.6</v>
+      </c>
       <c r="Y208" s="56"/>
       <c r="Z208" s="56"/>
       <c r="AA208" s="56"/>
@@ -27118,7 +27438,7 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ208" s="71" t="str">
         <f t="shared" si="10"/>
@@ -27206,7 +27526,9 @@
       <c r="X209" s="56">
         <v>8.5500000000000007</v>
       </c>
-      <c r="Y209" s="56"/>
+      <c r="Y209" s="56">
+        <v>8.75</v>
+      </c>
       <c r="Z209" s="56"/>
       <c r="AA209" s="56"/>
       <c r="AB209" s="56"/>
@@ -27225,19 +27547,19 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ209" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>8.7099999999999991</v>
       </c>
       <c r="AR209" s="71">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>8.0801328816903997</v>
       </c>
-      <c r="AS209" s="71" t="str">
+      <c r="AS209" s="71">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0.62986711830959941</v>
       </c>
     </row>
     <row r="210" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27310,8 +27632,12 @@
       <c r="W210" s="56">
         <v>24.4</v>
       </c>
-      <c r="X210" s="56"/>
-      <c r="Y210" s="56"/>
+      <c r="X210" s="56">
+        <v>24</v>
+      </c>
+      <c r="Y210" s="56">
+        <v>25.4</v>
+      </c>
       <c r="Z210" s="56"/>
       <c r="AA210" s="56"/>
       <c r="AB210" s="56"/>
@@ -27330,11 +27656,11 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>13</v>
-      </c>
-      <c r="AQ210" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ210" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>25.049999999999994</v>
       </c>
       <c r="AR210" s="71" t="str">
         <f>IFERROR(VLOOKUP(A210,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
